--- a/product_upload/packages/35/file.xlsx
+++ b/product_upload/packages/35/file.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT101"/>
+  <dimension ref="A1:AU101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacture Name</t>
+          <t>Manufacturer Name</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -649,6 +649,11 @@
         </is>
       </c>
       <c r="AT1" t="inlineStr">
+        <is>
+          <t>Name / En</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -673,7 +678,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -844,6 +849,11 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
+          <t>ETOXA 60 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
           <t>SKU-D0F242045938</t>
         </is>
       </c>
@@ -867,7 +877,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1034,6 +1044,11 @@
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="inlineStr">
         <is>
+          <t>ETOXA 90 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
           <t>SKU-1CB109DC3333</t>
         </is>
       </c>
@@ -1057,7 +1072,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1228,6 +1243,11 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
+          <t>ETOXA 120 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
           <t>SKU-2A7B1EF07C46</t>
         </is>
       </c>
@@ -1251,7 +1271,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1414,6 +1434,11 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
+          <t>PLATEREL 5MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
           <t>SKU-E2C5C204E058</t>
         </is>
       </c>
@@ -1437,7 +1462,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1596,6 +1621,11 @@
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="inlineStr">
         <is>
+          <t>PLATEREL 10MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
           <t>SKU-9DFC1E7C28D0</t>
         </is>
       </c>
@@ -1619,7 +1649,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1778,6 +1808,11 @@
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="inlineStr">
         <is>
+          <t>QATPEN XR 150MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
           <t>SKU-EAB8922EFF1E</t>
         </is>
       </c>
@@ -1801,7 +1836,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1960,6 +1995,11 @@
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="inlineStr">
         <is>
+          <t>ZAHRA TABLET</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
           <t>SKU-F2849FE5A49C</t>
         </is>
       </c>
@@ -1983,7 +2023,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2146,6 +2186,11 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
+          <t>PENTHROX 99.9 % liquid for inhalation</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
           <t>SKU-3A3C16137E65</t>
         </is>
       </c>
@@ -2169,7 +2214,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2324,6 +2369,11 @@
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="inlineStr">
         <is>
+          <t>PENTHROX 99.9 % liquid for inhalation</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
           <t>SKU-C861D8A602A6</t>
         </is>
       </c>
@@ -2347,7 +2397,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2510,6 +2560,11 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
+          <t>PENTHROX 99.9 % liquid for inhalation</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
           <t>SKU-D0146598CB26</t>
         </is>
       </c>
@@ -2533,7 +2588,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2696,6 +2751,11 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
+          <t>MONTAS 4 mg Chewable Tablets</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
           <t>SKU-B342AB7B5EFE</t>
         </is>
       </c>
@@ -2719,7 +2779,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2882,6 +2942,11 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
+          <t>MONTAS 5 mg Chewable Tablets</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
           <t>SKU-2FDB724D3CD0</t>
         </is>
       </c>
@@ -2905,7 +2970,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3072,6 +3137,11 @@
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="inlineStr">
         <is>
+          <t>CONVENTIN 300 mg Capsule</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
           <t>SKU-B88802449BE7</t>
         </is>
       </c>
@@ -3095,7 +3165,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3266,6 +3336,11 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
+          <t>CONVENTIN 400 mg Capsule</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
           <t>SKU-E88873F76E74</t>
         </is>
       </c>
@@ -3289,7 +3364,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3452,6 +3527,11 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
+          <t>ZYTERO 12.5 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
           <t>SKU-E5AC84AFA152</t>
         </is>
       </c>
@@ -3475,7 +3555,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3634,6 +3714,11 @@
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="inlineStr">
         <is>
+          <t>ZYTERO 25 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
           <t>SKU-BDA5AC58FE75</t>
         </is>
       </c>
@@ -3657,7 +3742,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3816,6 +3901,11 @@
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="inlineStr">
         <is>
+          <t>LEVETAM 100 mg/ml Oral Solution</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
           <t>SKU-0D536DD44DD8</t>
         </is>
       </c>
@@ -3839,7 +3929,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -4002,6 +4092,11 @@
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="inlineStr">
         <is>
+          <t>APISAL 0.9% EYE-NOSE DROPS</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
           <t>SKU-24AF46374848</t>
         </is>
       </c>
@@ -4025,7 +4120,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4192,6 +4287,11 @@
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="inlineStr">
         <is>
+          <t>ATROSOL 250 mcg/2 ml nebuliser solution</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
           <t>SKU-2EB4CFC768CB</t>
         </is>
       </c>
@@ -4215,7 +4315,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4374,6 +4474,11 @@
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="inlineStr">
         <is>
+          <t>VIBRAMYCIN 100MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
           <t>SKU-25B1B9A29DB0</t>
         </is>
       </c>
@@ -4397,7 +4502,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4568,6 +4673,11 @@
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="inlineStr">
         <is>
+          <t>MICROLUT 0.03MG-TAB COATED TAB.</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
           <t>SKU-5B322C49DE66</t>
         </is>
       </c>
@@ -4591,7 +4701,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4762,6 +4872,11 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
+          <t>XALKORI 250MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
           <t>SKU-2351B36CB13B</t>
         </is>
       </c>
@@ -4785,7 +4900,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -4956,6 +5071,11 @@
       </c>
       <c r="AT24" t="inlineStr">
         <is>
+          <t>XALKORI 200MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
           <t>SKU-7469E67C2C05</t>
         </is>
       </c>
@@ -4979,7 +5099,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -5150,6 +5270,11 @@
       </c>
       <c r="AT25" t="inlineStr">
         <is>
+          <t>ZYTIGA 500 Film-coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
           <t>SKU-9A9745C74F1C</t>
         </is>
       </c>
@@ -5173,7 +5298,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -5344,6 +5469,11 @@
       </c>
       <c r="AT26" t="inlineStr">
         <is>
+          <t>TOBREX OPTH.OINT. 0.3%</t>
+        </is>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
           <t>SKU-EA3F898CBA75</t>
         </is>
       </c>
@@ -5367,7 +5497,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -5534,6 +5664,11 @@
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="inlineStr">
         <is>
+          <t>TOBREX OPTH.SOLUTION 0.3%</t>
+        </is>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
           <t>SKU-7C187851BD1A</t>
         </is>
       </c>
@@ -5557,7 +5692,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -5728,6 +5863,11 @@
       </c>
       <c r="AT28" t="inlineStr">
         <is>
+          <t>MAXITROL DROPS</t>
+        </is>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
           <t>SKU-F6FC4CF0107E</t>
         </is>
       </c>
@@ -5751,7 +5891,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -5918,6 +6058,11 @@
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="inlineStr">
         <is>
+          <t>VIGAMOX 0.5% OPHTHALMIC SOLUTION</t>
+        </is>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
           <t>SKU-218F2882E98D</t>
         </is>
       </c>
@@ -5941,7 +6086,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -6108,6 +6253,11 @@
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="inlineStr">
         <is>
+          <t>AZOPT 1%</t>
+        </is>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
           <t>SKU-43EB6FFE5197</t>
         </is>
       </c>
@@ -6131,7 +6281,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -6298,6 +6448,11 @@
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="inlineStr">
         <is>
+          <t>DUOTRAV EYE DROPS</t>
+        </is>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
           <t>SKU-5CB8DFACEFEF</t>
         </is>
       </c>
@@ -6321,7 +6476,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -6480,6 +6635,11 @@
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="inlineStr">
         <is>
+          <t>EPNONE 50 mg Tablet</t>
+        </is>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
           <t>SKU-6E9B346BF1D4</t>
         </is>
       </c>
@@ -6503,7 +6663,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -6662,6 +6822,11 @@
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="inlineStr">
         <is>
+          <t>VAROXA 10 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
           <t>SKU-02F03CCB8B47</t>
         </is>
       </c>
@@ -6685,7 +6850,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -6864,6 +7029,11 @@
       </c>
       <c r="AT34" t="inlineStr">
         <is>
+          <t xml:space="preserve">FORTEO 20 MCG per 80MCL </t>
+        </is>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
           <t>SKU-1456204618F4</t>
         </is>
       </c>
@@ -6887,7 +7057,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -7046,6 +7216,11 @@
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="inlineStr">
         <is>
+          <t>NEUROGAB 75 mg capsule</t>
+        </is>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
           <t>SKU-43B970FD3A8C</t>
         </is>
       </c>
@@ -7069,7 +7244,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -7232,6 +7407,11 @@
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="inlineStr">
         <is>
+          <t>SIMBRINZA DROPS SUSP</t>
+        </is>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
           <t>SKU-A99C26B0F629</t>
         </is>
       </c>
@@ -7255,7 +7435,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -7422,6 +7602,11 @@
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="inlineStr">
         <is>
+          <t>NEVANAC EYE DROP</t>
+        </is>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
           <t>SKU-F603C277EBB5</t>
         </is>
       </c>
@@ -7445,7 +7630,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -7614,6 +7799,11 @@
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="inlineStr">
         <is>
+          <t>DEPAKINE 200MG-ML SOLU.</t>
+        </is>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
           <t>SKU-BDA639ACB822</t>
         </is>
       </c>
@@ -7637,7 +7827,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -7804,6 +7994,11 @@
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="inlineStr">
         <is>
+          <t>SEVITENSE 40/10 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
           <t>SKU-DE02AA881480</t>
         </is>
       </c>
@@ -7827,7 +8022,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -7990,6 +8185,11 @@
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="inlineStr">
         <is>
+          <t>SEVITENSE 20/10 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
           <t>SKU-D8D1C4978D42</t>
         </is>
       </c>
@@ -8013,7 +8213,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -8184,6 +8384,11 @@
       </c>
       <c r="AT41" t="inlineStr">
         <is>
+          <t>SEVITENSE 20/5 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
           <t>SKU-46D6F22C6B35</t>
         </is>
       </c>
@@ -8207,7 +8412,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -8370,6 +8575,11 @@
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="inlineStr">
         <is>
+          <t>SEVITENSE PLUS 40/10/12.5 MG FILM COATED  TABLET</t>
+        </is>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
           <t>SKU-0FFD892DACC6</t>
         </is>
       </c>
@@ -8393,7 +8603,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -8564,6 +8774,11 @@
       </c>
       <c r="AT43" t="inlineStr">
         <is>
+          <t>SEVITENSE PLUS 40/5/25 MG FILM COATED  TABLET</t>
+        </is>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
           <t>SKU-EA217F263B53</t>
         </is>
       </c>
@@ -8587,7 +8802,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -8758,6 +8973,11 @@
       </c>
       <c r="AT44" t="inlineStr">
         <is>
+          <t>SEVITENSE PLUS 40/10/25 MG FILM COATED  TABLET</t>
+        </is>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
           <t>SKU-CC9A98570494</t>
         </is>
       </c>
@@ -8781,7 +9001,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -8952,6 +9172,11 @@
       </c>
       <c r="AT45" t="inlineStr">
         <is>
+          <t>SEVITENSE PLUS 40/5/12.5 MG FILM COATED  TABLET</t>
+        </is>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
           <t>SKU-1DFBC5543F04</t>
         </is>
       </c>
@@ -8975,7 +9200,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -9146,6 +9371,11 @@
       </c>
       <c r="AT46" t="inlineStr">
         <is>
+          <t>SEVITENSE PLUS 20/5/12.5 MG FILM COATED  TABLET</t>
+        </is>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
           <t>SKU-E7400DD9C4CC</t>
         </is>
       </c>
@@ -9169,7 +9399,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -9328,6 +9558,11 @@
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="inlineStr">
         <is>
+          <t>DIVIDO 75MG DUAL RELEASE CAP</t>
+        </is>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
           <t>SKU-D832E2AA3324</t>
         </is>
       </c>
@@ -9351,7 +9586,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -9518,6 +9753,11 @@
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="inlineStr">
         <is>
+          <t>COUFATEX 1 mg Tablet</t>
+        </is>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
           <t>SKU-9CE682143C0C</t>
         </is>
       </c>
@@ -9541,7 +9781,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -9712,6 +9952,11 @@
       </c>
       <c r="AT49" t="inlineStr">
         <is>
+          <t>COUFATEX 2 mg Tablet</t>
+        </is>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
           <t>SKU-5A4DEC345062</t>
         </is>
       </c>
@@ -9735,7 +9980,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -9906,6 +10151,11 @@
       </c>
       <c r="AT50" t="inlineStr">
         <is>
+          <t>COUFATEX 5 mg Tablet</t>
+        </is>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
           <t>SKU-93D66E047DF8</t>
         </is>
       </c>
@@ -9929,7 +10179,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -10096,6 +10346,11 @@
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="inlineStr">
         <is>
+          <t>SEVITENSE 40/5 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
           <t>SKU-7ABFD28E10B1</t>
         </is>
       </c>
@@ -10119,7 +10374,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -10282,6 +10537,11 @@
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="inlineStr">
         <is>
+          <t>AZARGA EYE DROPS</t>
+        </is>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
           <t>SKU-27E1A4A4B87C</t>
         </is>
       </c>
@@ -10305,7 +10565,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -10482,6 +10742,11 @@
       </c>
       <c r="AT53" t="inlineStr">
         <is>
+          <t>EMCAST 5 MG CHEWABLE TABLET</t>
+        </is>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
           <t>SKU-A892798C5997</t>
         </is>
       </c>
@@ -10505,7 +10770,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -10678,6 +10943,11 @@
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="inlineStr">
         <is>
+          <t>EMCAST 4 MG CHEWABLE TABLET</t>
+        </is>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
           <t>SKU-96FEEF641D24</t>
         </is>
       </c>
@@ -10701,7 +10971,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -10878,6 +11148,11 @@
       </c>
       <c r="AT55" t="inlineStr">
         <is>
+          <t xml:space="preserve">EMCAST 10 MG </t>
+        </is>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
           <t>SKU-B910AEFC7A4A</t>
         </is>
       </c>
@@ -10901,7 +11176,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -11072,6 +11347,11 @@
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="inlineStr">
         <is>
+          <t>PILOCIN</t>
+        </is>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
           <t>SKU-9A4A6786FA41</t>
         </is>
       </c>
@@ -11095,7 +11375,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -11258,6 +11538,11 @@
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="inlineStr">
         <is>
+          <t>SYSTANE ULTRA UD LUBRICANT EYE DROPS</t>
+        </is>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
           <t>SKU-E3844DBCBD40</t>
         </is>
       </c>
@@ -11281,7 +11566,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -11440,6 +11725,11 @@
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="inlineStr">
         <is>
+          <t>PREGALEN 50 MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
           <t>SKU-B755FA8B33BE</t>
         </is>
       </c>
@@ -11463,7 +11753,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -11626,6 +11916,11 @@
       </c>
       <c r="AT59" t="inlineStr">
         <is>
+          <t>PREGALEN 50 MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
           <t>SKU-64793C4EBA63</t>
         </is>
       </c>
@@ -11649,7 +11944,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -11808,6 +12103,11 @@
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="inlineStr">
         <is>
+          <t>PREGALEN 150 MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
           <t>SKU-31F12CCA8BBA</t>
         </is>
       </c>
@@ -11831,7 +12131,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -11990,6 +12290,11 @@
       <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="inlineStr">
         <is>
+          <t>PREGALEN 150 MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
           <t>SKU-70BF8800AB2A</t>
         </is>
       </c>
@@ -12013,7 +12318,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -12184,6 +12489,11 @@
       </c>
       <c r="AT62" t="inlineStr">
         <is>
+          <t>RENOMER 800 MG FILM-COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
           <t>SKU-9E3E524A5611</t>
         </is>
       </c>
@@ -12207,7 +12517,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -12366,6 +12676,11 @@
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="inlineStr">
         <is>
+          <t>PREGALEN 75 MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
           <t>SKU-368641CB97AF</t>
         </is>
       </c>
@@ -12389,7 +12704,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -12548,6 +12863,11 @@
       <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="inlineStr">
         <is>
+          <t>OXIRA 8MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
           <t>SKU-80A4F3D20046</t>
         </is>
       </c>
@@ -12571,7 +12891,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -12730,6 +13050,11 @@
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="inlineStr">
         <is>
+          <t>VALDATIN 50MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
           <t>SKU-DB5B8FA3E70D</t>
         </is>
       </c>
@@ -12753,7 +13078,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -12912,6 +13237,11 @@
       <c r="AS66" t="inlineStr"/>
       <c r="AT66" t="inlineStr">
         <is>
+          <t>VALDATIN 50MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
           <t>SKU-A3CE00C85E30</t>
         </is>
       </c>
@@ -12935,7 +13265,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -13098,6 +13428,11 @@
       </c>
       <c r="AT67" t="inlineStr">
         <is>
+          <t>XEMETAN 25MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
           <t>SKU-F891698C0887</t>
         </is>
       </c>
@@ -13121,7 +13456,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -13284,6 +13619,11 @@
       </c>
       <c r="AT68" t="inlineStr">
         <is>
+          <t>PREGALEN 75 MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
           <t>SKU-383CAA7E8B78</t>
         </is>
       </c>
@@ -13307,7 +13647,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -13470,6 +13810,11 @@
       </c>
       <c r="AT69" t="inlineStr">
         <is>
+          <t>EPITAM 500MG PROLONGED RELEASE TABLET</t>
+        </is>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
           <t>SKU-FCAE226D8063</t>
         </is>
       </c>
@@ -13493,7 +13838,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -13656,6 +14001,11 @@
       <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="inlineStr">
         <is>
+          <t>MUCOSOLVAN 15MG-5ML ORAL LIQUID</t>
+        </is>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
           <t>SKU-09A7092BEEDD</t>
         </is>
       </c>
@@ -13679,7 +14029,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -13850,6 +14200,11 @@
       <c r="AS71" t="inlineStr"/>
       <c r="AT71" t="inlineStr">
         <is>
+          <t>PROXEN F.C. TAB 250MG</t>
+        </is>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
           <t>SKU-BF35194DE804</t>
         </is>
       </c>
@@ -13873,7 +14228,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -14048,6 +14403,11 @@
       </c>
       <c r="AT72" t="inlineStr">
         <is>
+          <t>PROXEN F.C TAB 500MG</t>
+        </is>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
           <t>SKU-FAEA6D7ED572</t>
         </is>
       </c>
@@ -14071,7 +14431,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -14240,6 +14600,11 @@
       <c r="AS73" t="inlineStr"/>
       <c r="AT73" t="inlineStr">
         <is>
+          <t>REGULON</t>
+        </is>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
           <t>SKU-12A9EF0B8735</t>
         </is>
       </c>
@@ -14263,7 +14628,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -14430,6 +14795,11 @@
       <c r="AS74" t="inlineStr"/>
       <c r="AT74" t="inlineStr">
         <is>
+          <t>VALIP 2 mg  film-coated tablets</t>
+        </is>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
           <t>SKU-83A496F5FD7F</t>
         </is>
       </c>
@@ -14453,7 +14823,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -14624,6 +14994,11 @@
       </c>
       <c r="AT75" t="inlineStr">
         <is>
+          <t>VALIP 4 mg  film-coated tablets</t>
+        </is>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
           <t>SKU-30CE1F2C80BB</t>
         </is>
       </c>
@@ -14647,7 +15022,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -14810,6 +15185,11 @@
       </c>
       <c r="AT76" t="inlineStr">
         <is>
+          <t>ROSUVAS 10 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
           <t>SKU-C44029384BBD</t>
         </is>
       </c>
@@ -14833,7 +15213,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -14992,6 +15372,11 @@
       <c r="AS77" t="inlineStr"/>
       <c r="AT77" t="inlineStr">
         <is>
+          <t>ROSUVAS 20 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
           <t>SKU-D4C603656C42</t>
         </is>
       </c>
@@ -15015,7 +15400,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -15178,6 +15563,11 @@
       </c>
       <c r="AT78" t="inlineStr">
         <is>
+          <t>EPITAM 750MG PROLONGED RELEASE TABLET</t>
+        </is>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
           <t>SKU-36610938A588</t>
         </is>
       </c>
@@ -15201,7 +15591,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -15376,6 +15766,11 @@
       </c>
       <c r="AT79" t="inlineStr">
         <is>
+          <t xml:space="preserve">TREMFYA 100 MG/ML </t>
+        </is>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
           <t>SKU-B370B893B5C7</t>
         </is>
       </c>
@@ -15399,7 +15794,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -15558,6 +15953,11 @@
       <c r="AS80" t="inlineStr"/>
       <c r="AT80" t="inlineStr">
         <is>
+          <t>ZONAM 2 MG FILM-COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
           <t>SKU-32C69E20C6A8</t>
         </is>
       </c>
@@ -15581,7 +15981,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -15740,6 +16140,11 @@
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="inlineStr">
         <is>
+          <t>ZONAM 1 MG FILM-COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
           <t>SKU-4749C7405543</t>
         </is>
       </c>
@@ -15763,7 +16168,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -15926,6 +16331,11 @@
       </c>
       <c r="AT82" t="inlineStr">
         <is>
+          <t>ESBRIET 267 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
           <t>SKU-AA6464B9B27D</t>
         </is>
       </c>
@@ -15949,7 +16359,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -16120,6 +16530,11 @@
       </c>
       <c r="AT83" t="inlineStr">
         <is>
+          <t>ESBRIET 801 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
           <t>SKU-AB30EC66F1BC</t>
         </is>
       </c>
@@ -16143,7 +16558,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -16306,6 +16721,11 @@
       <c r="AS84" t="inlineStr"/>
       <c r="AT84" t="inlineStr">
         <is>
+          <t>LONSURF</t>
+        </is>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
           <t>SKU-A2C08704D5DB</t>
         </is>
       </c>
@@ -16329,7 +16749,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -16492,6 +16912,11 @@
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="inlineStr">
         <is>
+          <t>LONSURF</t>
+        </is>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
           <t>SKU-645F50ECF0A1</t>
         </is>
       </c>
@@ -16515,7 +16940,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -16678,6 +17103,11 @@
       </c>
       <c r="AT86" t="inlineStr">
         <is>
+          <t>LEROXO 8 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
           <t>SKU-0804E766EDF1</t>
         </is>
       </c>
@@ -16701,7 +17131,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -16868,6 +17298,11 @@
       <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="inlineStr">
         <is>
+          <t>ZONAM 3 MG FILM-COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
           <t>SKU-3221DA3B0B56</t>
         </is>
       </c>
@@ -16891,7 +17326,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -17062,6 +17497,11 @@
       <c r="AS88" t="inlineStr"/>
       <c r="AT88" t="inlineStr">
         <is>
+          <t>HUMALOG KWIK-PEN MIX 50</t>
+        </is>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
           <t>SKU-C8E594F512AF</t>
         </is>
       </c>
@@ -17085,7 +17525,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -17260,6 +17700,11 @@
       </c>
       <c r="AT89" t="inlineStr">
         <is>
+          <t>OFEV 100 mg Soft Capsule</t>
+        </is>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
           <t>SKU-B15626EC991B</t>
         </is>
       </c>
@@ -17283,7 +17728,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -17450,6 +17895,11 @@
       <c r="AS90" t="inlineStr"/>
       <c r="AT90" t="inlineStr">
         <is>
+          <t>DESIRETT 75 mcg Film-Coated Tablets</t>
+        </is>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
           <t>SKU-477952640EA9</t>
         </is>
       </c>
@@ -17473,7 +17923,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -17640,6 +18090,11 @@
       <c r="AS91" t="inlineStr"/>
       <c r="AT91" t="inlineStr">
         <is>
+          <t>RESPRED 15 mg/5 ml syrup</t>
+        </is>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
           <t>SKU-CC66E961715B</t>
         </is>
       </c>
@@ -17663,7 +18118,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -17834,6 +18289,11 @@
       </c>
       <c r="AT92" t="inlineStr">
         <is>
+          <t>RESPRED 5 mg/5 ml syrup</t>
+        </is>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
           <t>SKU-71187B9A29F3</t>
         </is>
       </c>
@@ -17857,7 +18317,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -18012,6 +18472,11 @@
       <c r="AS93" t="inlineStr"/>
       <c r="AT93" t="inlineStr">
         <is>
+          <t>VITA-D 50000 IU Tablet</t>
+        </is>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
           <t>SKU-830551B9213D</t>
         </is>
       </c>
@@ -18035,7 +18500,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -18210,6 +18675,11 @@
       </c>
       <c r="AT94" t="inlineStr">
         <is>
+          <t>CLOPACIN 75mg film-coated tablets</t>
+        </is>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
           <t>SKU-E642C3007847</t>
         </is>
       </c>
@@ -18233,7 +18703,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -18392,6 +18862,11 @@
       <c r="AS95" t="inlineStr"/>
       <c r="AT95" t="inlineStr">
         <is>
+          <t>LYSTEDA 650 mg Tablet</t>
+        </is>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
           <t>SKU-8E294BF773FA</t>
         </is>
       </c>
@@ -18415,7 +18890,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -18586,6 +19061,11 @@
       <c r="AS96" t="inlineStr"/>
       <c r="AT96" t="inlineStr">
         <is>
+          <t>MOVIPREP POWDER FOR ORAL SOLUTION</t>
+        </is>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
           <t>SKU-86D28CED5003</t>
         </is>
       </c>
@@ -18609,7 +19089,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -18778,6 +19258,11 @@
       <c r="AS97" t="inlineStr"/>
       <c r="AT97" t="inlineStr">
         <is>
+          <t>COAPROVEL 300-12.5 MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
           <t>SKU-CF95D2E193F1</t>
         </is>
       </c>
@@ -18801,7 +19286,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -18970,6 +19455,11 @@
       </c>
       <c r="AT98" t="inlineStr">
         <is>
+          <t>RELPAX 20MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
           <t>SKU-21E9F2C8465E</t>
         </is>
       </c>
@@ -18993,7 +19483,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -19158,6 +19648,11 @@
       <c r="AS99" t="inlineStr"/>
       <c r="AT99" t="inlineStr">
         <is>
+          <t>RELPAX 20MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
           <t>SKU-EFF705794B97</t>
         </is>
       </c>
@@ -19181,7 +19676,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -19358,6 +19853,11 @@
       </c>
       <c r="AT100" t="inlineStr">
         <is>
+          <t>RELPAX 40MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
           <t>SKU-8AC42C02B5DD</t>
         </is>
       </c>
@@ -19381,7 +19881,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -19553,6 +20053,11 @@
       </c>
       <c r="AS101" t="inlineStr"/>
       <c r="AT101" t="inlineStr">
+        <is>
+          <t>RELPAX 40MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU101" t="inlineStr">
         <is>
           <t>SKU-7DCB5E2F3449</t>
         </is>
@@ -19569,7 +20074,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB12"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19615,100 +20120,105 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Level 1*</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Level 2*</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Level 3*</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Risk Class *</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Sterility</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Model / Catalogue Number</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Single Use</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Legal Manufacturer</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>UDI-DI</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>GMDN Code / Term</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>SFDA Authorized Representative License No.</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Power Source</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Warranty</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Storage Conditions / En</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Branch id</t>
         </is>
@@ -19740,7 +20250,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -19755,92 +20265,97 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>SKU-98681</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>162.71</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T2" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" t="n">
+        <v>297</v>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>100</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>12</v>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19872,7 +20387,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -19887,92 +20402,97 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>SKU-76396</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>57.13</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T3" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" t="n">
+        <v>298</v>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>100</v>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>12</v>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20004,7 +20524,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -20019,92 +20539,97 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>SKU-77585</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>366.12</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T4" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U4" t="inlineStr">
+      <c r="U4" t="n">
+        <v>299</v>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>100</v>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>12</v>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20136,7 +20661,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -20151,92 +20676,97 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>SKU-97235</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>287.58</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T5" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U5" t="inlineStr">
+      <c r="U5" t="n">
+        <v>300</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>100</v>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>12</v>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20268,7 +20798,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -20283,92 +20813,97 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>SKU-94306</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>442.83</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T6" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U6" t="inlineStr">
+      <c r="U6" t="n">
+        <v>301</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>100</v>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>12</v>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20400,7 +20935,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -20415,92 +20950,97 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>SKU-48511</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>18.77</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T7" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U7" t="inlineStr">
+      <c r="U7" t="n">
+        <v>302</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>100</v>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>12</v>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20532,7 +21072,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -20547,92 +21087,97 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>SKU-59827</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>20.01</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T8" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U8" t="inlineStr">
+      <c r="U8" t="n">
+        <v>303</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>100</v>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>12</v>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20664,7 +21209,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -20679,92 +21224,97 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>SKU-10646</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>353.76</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T9" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U9" t="inlineStr">
+      <c r="U9" t="n">
+        <v>304</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>100</v>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>12</v>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20796,7 +21346,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -20811,92 +21361,97 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>SKU-75621</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>32.68</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T10" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U10" t="inlineStr">
+      <c r="U10" t="n">
+        <v>305</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>100</v>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>12</v>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20928,7 +21483,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -20943,92 +21498,97 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>SKU-15580</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>70.18000000000001</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T11" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U11" t="inlineStr">
+      <c r="U11" t="n">
+        <v>306</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>100</v>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>12</v>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21060,7 +21620,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -21075,92 +21635,97 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>SKU-57955</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>407.56</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Thermometer</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T12" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U12" t="inlineStr">
+      <c r="U12" t="n">
+        <v>307</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>100</v>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
         <v>12</v>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21177,7 +21742,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21283,6 +21848,16 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Ingredients</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
@@ -21318,7 +21893,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -21383,6 +21958,16 @@
         </is>
       </c>
       <c r="U2" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>SKU-E6FE37F6CE22</t>
         </is>
@@ -21419,7 +22004,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -21484,6 +22069,16 @@
         </is>
       </c>
       <c r="U3" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>SKU-F49F5E31CEDF</t>
         </is>
@@ -21520,7 +22115,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -21585,6 +22180,16 @@
         </is>
       </c>
       <c r="U4" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>SKU-2EBE414A546E</t>
         </is>
@@ -21621,7 +22226,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -21686,6 +22291,16 @@
         </is>
       </c>
       <c r="U5" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>SKU-5106FFE5D1B8</t>
         </is>
@@ -21722,7 +22337,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -21787,6 +22402,16 @@
         </is>
       </c>
       <c r="U6" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
         <is>
           <t>SKU-A0880B0FE98D</t>
         </is>
@@ -21823,7 +22448,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -21888,6 +22513,16 @@
         </is>
       </c>
       <c r="U7" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>SKU-C1EFCA88AC75</t>
         </is>
@@ -21924,7 +22559,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -21989,6 +22624,16 @@
         </is>
       </c>
       <c r="U8" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
         <is>
           <t>SKU-B82C5A6D1001</t>
         </is>
@@ -22025,7 +22670,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -22090,6 +22735,16 @@
         </is>
       </c>
       <c r="U9" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
         <is>
           <t>SKU-D001595BBA38</t>
         </is>
@@ -22126,7 +22781,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -22191,6 +22846,16 @@
         </is>
       </c>
       <c r="U10" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
         <is>
           <t>SKU-F25D4C8C0888</t>
         </is>
@@ -22227,7 +22892,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -22292,6 +22957,16 @@
         </is>
       </c>
       <c r="U11" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
         <is>
           <t>SKU-F79439FE80BA</t>
         </is>
@@ -22328,7 +23003,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -22393,6 +23068,16 @@
         </is>
       </c>
       <c r="U12" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
         <is>
           <t>SKU-DA6DE939E69F</t>
         </is>
@@ -22429,7 +23114,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -22494,6 +23179,16 @@
         </is>
       </c>
       <c r="U13" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
         <is>
           <t>SKU-33BDA9C66838</t>
         </is>
@@ -22530,7 +23225,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -22595,6 +23290,16 @@
         </is>
       </c>
       <c r="U14" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
         <is>
           <t>SKU-D4EB43C6D2C7</t>
         </is>
@@ -22631,7 +23336,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -22696,6 +23401,16 @@
         </is>
       </c>
       <c r="U15" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
         <is>
           <t>SKU-664D465779F2</t>
         </is>
@@ -22732,7 +23447,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -22797,6 +23512,16 @@
         </is>
       </c>
       <c r="U16" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
         <is>
           <t>SKU-A10ECE622B0C</t>
         </is>
@@ -22833,7 +23558,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -22898,6 +23623,16 @@
         </is>
       </c>
       <c r="U17" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
         <is>
           <t>SKU-E1AE1515FBD9</t>
         </is>
@@ -22934,7 +23669,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -22999,6 +23734,16 @@
         </is>
       </c>
       <c r="U18" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
         <is>
           <t>SKU-31E4D4BAECD2</t>
         </is>
@@ -23035,7 +23780,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -23100,6 +23845,16 @@
         </is>
       </c>
       <c r="U19" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
         <is>
           <t>SKU-64B44A169557</t>
         </is>
@@ -23136,7 +23891,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -23201,6 +23956,16 @@
         </is>
       </c>
       <c r="U20" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
         <is>
           <t>SKU-C6E134BDE9B0</t>
         </is>
@@ -23237,7 +24002,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -23302,6 +24067,16 @@
         </is>
       </c>
       <c r="U21" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
         <is>
           <t>SKU-59770301DDFF</t>
         </is>

--- a/product_upload/packages/35/file.xlsx
+++ b/product_upload/packages/35/file.xlsx
@@ -1279,8 +1279,16 @@
           <t>8665353360-581-401262903508</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PLATEREL 5MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>PLATEREL 5MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
@@ -1470,8 +1478,16 @@
           <t>2445278580-590-817214423365</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PLATEREL 10MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>PLATEREL 10MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
@@ -1657,8 +1673,16 @@
           <t>5352824961-591-627662839678</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ QATPEN XR 150MG TABLETS</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>QATPEN XR 150MG TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
@@ -1844,8 +1868,16 @@
           <t>9924096449-901-848907862936</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ZAHRA TABLET</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>ZAHRA TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
@@ -2031,8 +2063,16 @@
           <t>8566629354-596-295238463003</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PENTHROX 99.9 % liquid for inhalation</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>PENTHROX 99.9 % liquid for inhalation detailed description.</t>
+        </is>
+      </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
@@ -2222,8 +2262,16 @@
           <t>1102276619-444-051799659724</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PENTHROX 99.9 % liquid for inhalation</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>PENTHROX 99.9 % liquid for inhalation detailed description.</t>
+        </is>
+      </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
@@ -2405,8 +2453,16 @@
           <t>9423695070-101-145249633263</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PENTHROX 99.9 % liquid for inhalation</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>PENTHROX 99.9 % liquid for inhalation detailed description.</t>
+        </is>
+      </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
@@ -2596,8 +2652,16 @@
           <t>2213530754-210-763859060283</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ MONTAS 4 mg Chewable Tablets</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>MONTAS 4 mg Chewable Tablets detailed description.</t>
+        </is>
+      </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
@@ -2787,8 +2851,16 @@
           <t>8043915975-595-619580203356</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ MONTAS 5 mg Chewable Tablets</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>MONTAS 5 mg Chewable Tablets detailed description.</t>
+        </is>
+      </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
@@ -3372,8 +3444,16 @@
           <t>2096557946-678-158387482808</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ZYTERO 12.5 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>ZYTERO 12.5 mg Film Coated Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
@@ -3563,8 +3643,16 @@
           <t>4254789052-985-983886372391</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ZYTERO 25 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>ZYTERO 25 mg Film Coated Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
@@ -3750,8 +3838,16 @@
           <t>9525322015-969-396250577976</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LEVETAM 100 mg/ml Oral Solution</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>LEVETAM 100 mg/ml Oral Solution detailed description.</t>
+        </is>
+      </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
@@ -4323,8 +4419,16 @@
           <t>6705635079-399-980441013585</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ VIBRAMYCIN 100MG TABLET</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>VIBRAMYCIN 100MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
@@ -6484,8 +6588,16 @@
           <t>7134233244-685-565274422111</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ EPNONE 50 mg Tablet</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>EPNONE 50 mg Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
@@ -6671,8 +6783,16 @@
           <t>7086964121-422-327852078487</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ VAROXA 10 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>VAROXA 10 mg Film Coated Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
@@ -7065,8 +7185,16 @@
           <t>6262100217-529-781877107365</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ NEUROGAB 75 mg capsule</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>NEUROGAB 75 mg capsule detailed description.</t>
+        </is>
+      </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
@@ -9407,8 +9535,16 @@
           <t>1256340399-734-460462386225</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DIVIDO 75MG DUAL RELEASE CAP</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>DIVIDO 75MG DUAL RELEASE CAP detailed description.</t>
+        </is>
+      </c>
       <c r="I47" t="n">
         <v>0</v>
       </c>
@@ -11574,8 +11710,16 @@
           <t>0504559531-191-058152624333</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PREGALEN 50 MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>PREGALEN 50 MG CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I58" t="n">
         <v>0</v>
       </c>
@@ -11761,8 +11905,16 @@
           <t>6983227150-468-056943607018</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PREGALEN 50 MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>PREGALEN 50 MG CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I59" t="n">
         <v>0</v>
       </c>
@@ -11952,8 +12104,16 @@
           <t>7351598092-839-713036578427</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PREGALEN 150 MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>PREGALEN 150 MG CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I60" t="n">
         <v>0</v>
       </c>
@@ -12139,8 +12299,16 @@
           <t>5234183792-472-886625472698</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PREGALEN 150 MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>PREGALEN 150 MG CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
@@ -12525,8 +12693,16 @@
           <t>6138166663-948-300850415869</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PREGALEN 75 MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>PREGALEN 75 MG CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I63" t="n">
         <v>0</v>
       </c>
@@ -12712,8 +12888,16 @@
           <t>9642371050-382-731377636853</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ OXIRA 8MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>OXIRA 8MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I64" t="n">
         <v>0</v>
       </c>
@@ -12899,8 +13083,16 @@
           <t>9574540312-102-023421490980</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ VALDATIN 50MG TABLET</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>VALDATIN 50MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I65" t="n">
         <v>0</v>
       </c>
@@ -13086,8 +13278,16 @@
           <t>3532262632-632-679055407962</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ VALDATIN 50MG TABLET</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>VALDATIN 50MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I66" t="n">
         <v>0</v>
       </c>
@@ -13273,8 +13473,16 @@
           <t>6766107600-192-445215181246</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ XEMETAN 25MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>XEMETAN 25MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I67" t="n">
         <v>0</v>
       </c>
@@ -13464,8 +13672,16 @@
           <t>0245163695-132-167223046584</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PREGALEN 75 MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>PREGALEN 75 MG CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I68" t="n">
         <v>0</v>
       </c>
@@ -13655,8 +13871,16 @@
           <t>6472542683-522-368557141582</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ EPITAM 500MG PROLONGED RELEASE TABLET</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>EPITAM 500MG PROLONGED RELEASE TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I69" t="n">
         <v>0</v>
       </c>
@@ -13846,8 +14070,16 @@
           <t>0301899579-346-023106595927</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ MUCOSOLVAN 15MG-5ML ORAL LIQUID</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>MUCOSOLVAN 15MG-5ML ORAL LIQUID detailed description.</t>
+        </is>
+      </c>
       <c r="I70" t="n">
         <v>0</v>
       </c>
@@ -15030,8 +15262,16 @@
           <t>9152180398-864-403827349959</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ROSUVAS 10 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>ROSUVAS 10 MG FILM COATED TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I76" t="n">
         <v>0</v>
       </c>
@@ -15221,8 +15461,16 @@
           <t>0515142514-542-413713639771</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ROSUVAS 20 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>ROSUVAS 20 MG FILM COATED TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I77" t="n">
         <v>0</v>
       </c>
@@ -15408,8 +15656,16 @@
           <t>1938563882-436-526893649442</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ EPITAM 750MG PROLONGED RELEASE TABLET</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>EPITAM 750MG PROLONGED RELEASE TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I78" t="n">
         <v>0</v>
       </c>
@@ -15802,8 +16058,16 @@
           <t>6406397216-011-763723514352</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ZONAM 2 MG FILM-COATED TABLET</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>ZONAM 2 MG FILM-COATED TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I80" t="n">
         <v>0</v>
       </c>
@@ -15989,8 +16253,16 @@
           <t>3364718921-039-041328856088</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ZONAM 1 MG FILM-COATED TABLET</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>ZONAM 1 MG FILM-COATED TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I81" t="n">
         <v>0</v>
       </c>
@@ -16176,8 +16448,16 @@
           <t>3438950924-781-890746272042</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ESBRIET 267 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>ESBRIET 267 MG FILM COATED TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I82" t="n">
         <v>0</v>
       </c>
@@ -16566,8 +16846,16 @@
           <t>4173617489-729-271354068443</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LONSURF</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>LONSURF detailed description.</t>
+        </is>
+      </c>
       <c r="I84" t="n">
         <v>0</v>
       </c>
@@ -16757,8 +17045,16 @@
           <t>8035190847-648-397445933355</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LONSURF</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>LONSURF detailed description.</t>
+        </is>
+      </c>
       <c r="I85" t="n">
         <v>0</v>
       </c>
@@ -16948,8 +17244,16 @@
           <t>8617701553-649-159334330993</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LEROXO 8 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>LEROXO 8 MG FILM COATED TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I86" t="n">
         <v>0</v>
       </c>
@@ -18325,8 +18629,16 @@
           <t>5347696228-960-842361595581</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ VITA-D 50000 IU Tablet</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>VITA-D 50000 IU Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I93" t="n">
         <v>0</v>
       </c>
@@ -18711,8 +19023,16 @@
           <t>7195038022-170-723321183306</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LYSTEDA 650 mg Tablet</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>LYSTEDA 650 mg Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I95" t="n">
         <v>0</v>
       </c>
@@ -19294,8 +19614,16 @@
           <t>0878690332-054-920903310842</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ RELPAX 20MG TABLET</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>RELPAX 20MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I98" t="inlineStr">
         <is>
           <t>PFIZER SAUDI LIMITED</t>
@@ -19491,8 +19819,16 @@
           <t>2180726239-962-791577209715</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ RELPAX 20MG TABLET</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>RELPAX 20MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I99" t="inlineStr">
         <is>
           <t>PFIZER SAUDI LIMITED</t>

--- a/product_upload/packages/35/file.xlsx
+++ b/product_upload/packages/35/file.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -20456,7 +20456,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -22078,7 +22078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:X21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22159,40 +22159,45 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>Size unit</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>Manufacturer *</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Period After Opening.1</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Warnings</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Manufacturer Name</t>
-        </is>
-      </c>
       <c r="V1" t="inlineStr">
         <is>
+          <t>Manufacturer</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Ingredients</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -22272,38 +22277,43 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>402.02</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>SKU-E6FE37F6CE22</t>
         </is>
@@ -22383,38 +22393,43 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>69.56</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>SKU-F49F5E31CEDF</t>
         </is>
@@ -22494,38 +22509,43 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>163.65</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>SKU-2EBE414A546E</t>
         </is>
@@ -22605,38 +22625,43 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>465.55</v>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>SKU-5106FFE5D1B8</t>
         </is>
@@ -22716,38 +22741,43 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>354.1</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>SKU-A0880B0FE98D</t>
         </is>
@@ -22827,38 +22857,43 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>35.46</v>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>SKU-C1EFCA88AC75</t>
         </is>
@@ -22938,38 +22973,43 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>453.07</v>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>SKU-B82C5A6D1001</t>
         </is>
@@ -23049,38 +23089,43 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>15.74</v>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>SKU-D001595BBA38</t>
         </is>
@@ -23160,38 +23205,43 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>27.76</v>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>SKU-F25D4C8C0888</t>
         </is>
@@ -23271,38 +23321,43 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>347.56</v>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>SKU-F79439FE80BA</t>
         </is>
@@ -23382,38 +23437,43 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>149.32</v>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>SKU-DA6DE939E69F</t>
         </is>
@@ -23493,38 +23553,43 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>357</v>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>SKU-33BDA9C66838</t>
         </is>
@@ -23604,38 +23669,43 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>229.47</v>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>SKU-D4EB43C6D2C7</t>
         </is>
@@ -23715,38 +23785,43 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>189.84</v>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>SKU-664D465779F2</t>
         </is>
@@ -23826,38 +23901,43 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>209.1</v>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>SKU-A10ECE622B0C</t>
         </is>
@@ -23937,38 +24017,43 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>460.07</v>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>SKU-E1AE1515FBD9</t>
         </is>
@@ -24048,38 +24133,43 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>243.81</v>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>SKU-31E4D4BAECD2</t>
         </is>
@@ -24159,38 +24249,43 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>251.44</v>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>SKU-64B44A169557</t>
         </is>
@@ -24270,38 +24365,43 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>109.08</v>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>SKU-C6E134BDE9B0</t>
         </is>
@@ -24381,38 +24481,43 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>62.44</v>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>SKU-59770301DDFF</t>
         </is>
